--- a/evals/unit_tests_comparative/test06_conv_gap_exceeds_roofline/analysis_output_ref/perf_report_trace1.xlsx
+++ b/evals/unit_tests_comparative/test06_conv_gap_exceeds_roofline/analysis_output_ref/perf_report_trace1.xlsx
@@ -11,9 +11,10 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CONV_fwd" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="diff_stats" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="diff_stats" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,485 +977,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>process_name</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>thread_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Input type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ex_UID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>operation_count</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>total_duration_us</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mean_duration_us</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>std_duration_us</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>GFLOPS</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Data Moved (MB)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>FLOPS/Byte</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Compute Spec</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Bound</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_mean</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_std</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_mean</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_std</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>speedup (trace2/trace1)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>delta_us (trace2 - trace1)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>lca_kernel_count_trace2</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>lca_id</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>lca_name</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>lca_total_kernel_time_trace1_us</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>lca_total_kernel_time_trace2_us</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_median</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_min</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_max</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_median</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_min</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_max</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_median</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_min</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_max</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Time (µs)_first</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_mean</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_median</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_std</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_min</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Pct Roofline_max</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details_summary</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>trunc_kernel_details</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>perf_params</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>has_perf_model</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>Cumulative Percentage (%)</t>
+          <t>call_stack</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>aten::convolution</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>CONV_fwd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>((4, 256, 56, 56), (512, 256, 3, 3), ())</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>('', '', '', '[1, 1]', '[1, 1]', '[1, 1]', 'False', '[0, 0]', '1')</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>29.601431552</v>
-      </c>
-      <c r="P2" t="n">
-        <v>20.6259765625</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1368.668528952228</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>COMPUTE_BOUND</t>
-        </is>
-      </c>
-      <c r="T2" t="n">
-        <v>0.010813952</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>14.800715776</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1960</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>aten::convolution</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.010813952</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.010813952</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.010813952</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14.800715776</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>14.800715776</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.800715776</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>41.80993157062147</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.090496578531074</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.090496578531074</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>2.090496578531074</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.090496578531074</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'gpu_op_uid': 5, 'count': 1, 'total_duration_us': np.float64(2000.0), 'gpu_op_uids': [5], 'mean_duration_us': np.float64(2000.0), 'median_duration_us': np.float64(2000.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2000.0), 'max_duration_us': np.float64(2000.0)}]</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'mean_duration_us': np.float64(2000.0)}]</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>{'convNd': 'conv2d', 'input_shape': (4, 256, 56, 56), 'filter_shape': (512, 256, 3, 3), 'dtype_input_weight': ('c10::bfloat16', 'c10::bfloat16'), 'input_stride': None, 'weight_stride': None, 'bias': True, 'stride': (1, 1), 'padding': (1, 1), 'dilation': (1, 1), 'transposed_conv': False, 'output_padding': (0, 0), 'groups': 1}</t>
-        </is>
-      </c>
-      <c r="BC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>100</v>
+          <t>aten::convolution =&gt; aten::convolution</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:BF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1479,262 +1044,287 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>param: convNd</t>
+          <t>op category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>param: input_shape</t>
+          <t>process_name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>param: filter_shape</t>
+          <t>process_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_input_weight</t>
+          <t>thread_name</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: input_stride</t>
+          <t>Input Dims</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: weight_stride</t>
+          <t>Input type</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: bias</t>
+          <t>Input Strides</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>param: stride</t>
+          <t>Concrete Inputs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>param: padding</t>
+          <t>ex_UID</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>param: dilation</t>
+          <t>operation_count</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>param: transposed_conv</t>
+          <t>total_duration_us</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>param: output_padding</t>
+          <t>mean_duration_us</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>param: groups</t>
+          <t>std_duration_us</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>num_kernels</t>
+          <t>GFLOPS</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>Data Moved (MB)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>FLOPS/Byte</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Roofline Bound</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>speedup (trace2/trace1)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>delta_us (trace2 - trace1)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>lca_count_trace2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lca_id</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lca_name</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lca_total_kernel_time_trace1_us</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lca_total_kernel_time_trace2_us</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_median</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_min</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_max</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>TB/s_std</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_mean</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>TFLOPS/s_std</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>process_name_first</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>process_label_first</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>thread_name_first</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Compute Spec</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Roofline Time (µs)_first</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Roofline Bound_first</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_mean</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_median</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_std</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_min</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Pct Roofline_max</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details__summarize_kernel_stats</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details_summary</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims_first</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Input type_first</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides_first</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs_first</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>UID_first</t>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>perf_params</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>has_perf_model</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative Percentage (%)</t>
         </is>
       </c>
     </row>
@@ -1746,197 +1336,192 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>conv2d</t>
+          <t>CONV_fwd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(4, 256, 56, 56)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(512, 256, 3, 3)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>((4, 256, 56, 56), (512, 256, 3, 3), ())</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>('c10::bfloat16', 'c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>(1, 1)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>(1, 1)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>(1, 1)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>(0, 0)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>('', '', '', '[1, 1]', '[1, 1]', '[1, 1]', 'False', '[0, 0]', '1')</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>29.601431552</v>
       </c>
       <c r="P2" t="n">
-        <v>29.601431552</v>
+        <v>20.6259765625</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.6259765625</v>
-      </c>
-      <c r="R2" t="n">
         <v>1368.668528952228</v>
       </c>
-      <c r="S2" t="n">
-        <v>0.010813952</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>COMPUTE_BOUND</t>
+        </is>
       </c>
       <c r="T2" t="n">
         <v>0.010813952</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>14.800715776</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1960</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>aten::convolution</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.010813952</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AL2" t="n">
         <v>0.010813952</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AM2" t="n">
+        <v>0.010813952</v>
+      </c>
+      <c r="AN2" t="n">
         <v>14.800715776</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AO2" t="n">
         <v>14.800715776</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
+      <c r="AP2" t="n">
         <v>14.800715776</v>
       </c>
-      <c r="AB2" t="n">
-        <v>14.800715776</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>matrix_bf16</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AQ2" t="n">
         <v>41.80993157062147</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>COMPUTE_BOUND</t>
-        </is>
-      </c>
-      <c r="AI2" t="n">
+      <c r="AR2" t="n">
         <v>2.090496578531074</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AS2" t="n">
         <v>2.090496578531074</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
         <v>2.090496578531074</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>2.090496578531074</v>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'gpu_op_uid': 5, 'count': 1, 'total_duration_us': np.float64(2000.0), 'gpu_op_uids': [5], 'mean_duration_us': np.float64(2000.0), 'median_duration_us': np.float64(2000.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2000.0), 'max_duration_us': np.float64(2000.0)}]</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AW2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2000.0), 'gpu_op_uids': [5], 'mean_duration_us': np.float64(2000.0), 'median_duration_us': np.float64(2000.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2000.0), 'max_duration_us': np.float64(2000.0)}]</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'mean_duration_us': np.float64(2000.0)}]</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>[[4, 256, 56, 56], [512, 256, 3, 3], []]</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>['c10::bfloat16', 'c10::bfloat16', 'c10::bfloat16']</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>['', '', '', '[1, 1]', '[1, 1]', '[1, 1]', 'False', '[0, 0]', '1']</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AZ2" t="n">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>{'convNd': 'conv2d', 'input_shape': (4, 256, 56, 56), 'filter_shape': (512, 256, 3, 3), 'dtype_input_weight': ('c10::bfloat16', 'c10::bfloat16'), 'input_stride': None, 'weight_stride': None, 'bias': True, 'stride': (1, 1), 'padding': (1, 1), 'dilation': (1, 1), 'transposed_conv': False, 'output_padding': (0, 0), 'groups': 1}</t>
+        </is>
+      </c>
+      <c r="BC2" t="b">
         <v>1</v>
       </c>
-      <c r="BA2" t="n">
-        <v>1</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>aten::convolution =&gt; aten::convolution</t>
+        </is>
+      </c>
+      <c r="BE2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1950,6 +1535,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:BA2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: convNd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: input_shape</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: filter_shape</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_input_weight</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>param: input_stride</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>param: weight_stride</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>param: bias</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>param: stride</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>param: padding</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>param: dilation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>param: transposed_conv</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>param: output_padding</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>param: groups</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>num_kernels</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Roofline Time (µs)_first</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Roofline Bound_first</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_mean</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_median</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_std</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_min</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Pct Roofline_max</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::convolution</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>conv2d</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(4, 256, 56, 56)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(512, 256, 3, 3)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(1, 1)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(1, 1)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>(1, 1)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>29.601431552</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>20.6259765625</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1368.668528952228</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.010813952</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.010813952</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>0.010813952</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.010813952</v>
+      </c>
+      <c r="X2" t="n">
+        <v>14.800715776</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14.800715776</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>14.800715776</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14.800715776</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>matrix_bf16</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>41.80993157062147</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>COMPUTE_BOUND</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.090496578531074</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.090496578531074</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>2.090496578531074</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2.090496578531074</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2000.0), 'gpu_op_uids': [5], 'mean_duration_us': np.float64(2000.0), 'median_duration_us': np.float64(2000.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2000.0), 'max_duration_us': np.float64(2000.0)}]</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>[{'name': 'miopenConvolutionForwardAlgo_BwdDataB&lt;BF16, BF16, float, 3, 3&gt;', 'stream': 0, 'mean_duration_us': np.float64(2000.0)}]</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>[[4, 256, 56, 56], [512, 256, 3, 3], []]</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>['c10::bfloat16', 'c10::bfloat16', 'c10::bfloat16']</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>['', '', '', '[1, 1]', '[1, 1]', '[1, 1]', 'False', '[0, 0]', '1']</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
